--- a/docs/tables/FINAL_results.xlsx
+++ b/docs/tables/FINAL_results.xlsx
@@ -2352,7 +2352,7 @@
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t>inlier RMSE@3cm (cm)</t>
+          <t>inlier RMSE@3cm (mm)</t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
@@ -2445,7 +2445,7 @@
         <v>1.854</v>
       </c>
       <c r="S5" t="n">
-        <v>1.301</v>
+        <v>13.01</v>
       </c>
       <c r="T5" t="n">
         <v>100</v>
@@ -2529,7 +2529,7 @@
         <v>1.688</v>
       </c>
       <c r="S6" t="n">
-        <v>1.11</v>
+        <v>11.1</v>
       </c>
       <c r="T6" t="n">
         <v>100</v>
@@ -2613,7 +2613,7 @@
         <v>1.584</v>
       </c>
       <c r="S7" t="n">
-        <v>1.418</v>
+        <v>14.18</v>
       </c>
       <c r="T7" t="n">
         <v>100</v>
@@ -2697,7 +2697,7 @@
         <v>0.53</v>
       </c>
       <c r="S8" t="n">
-        <v>1.273</v>
+        <v>12.73</v>
       </c>
       <c r="T8" t="n">
         <v>100</v>
@@ -2781,7 +2781,7 @@
         <v>0.641</v>
       </c>
       <c r="S9" t="n">
-        <v>1.209</v>
+        <v>12.09</v>
       </c>
       <c r="T9" t="n">
         <v>100</v>
@@ -2865,7 +2865,7 @@
         <v>0.897</v>
       </c>
       <c r="S10" t="n">
-        <v>1.381</v>
+        <v>13.81</v>
       </c>
       <c r="T10" t="n">
         <v>100</v>
@@ -2949,7 +2949,7 @@
         <v>1.948</v>
       </c>
       <c r="S11" t="n">
-        <v>1.737</v>
+        <v>17.37</v>
       </c>
       <c r="T11" t="n">
         <v>100</v>
@@ -3033,7 +3033,7 @@
         <v>6.463</v>
       </c>
       <c r="S12" t="n">
-        <v>1.945</v>
+        <v>19.45</v>
       </c>
       <c r="T12" t="n">
         <v>95.8</v>
@@ -3117,7 +3117,7 @@
         <v>1.686</v>
       </c>
       <c r="S13" t="n">
-        <v>1.963</v>
+        <v>19.63</v>
       </c>
       <c r="T13" t="n">
         <v>100</v>
@@ -3201,7 +3201,7 @@
         <v>0.577</v>
       </c>
       <c r="S14" t="n">
-        <v>1.725</v>
+        <v>17.25</v>
       </c>
       <c r="T14" t="n">
         <v>100</v>
@@ -3285,7 +3285,7 @@
         <v>2.841</v>
       </c>
       <c r="S15" t="n">
-        <v>1.912</v>
+        <v>19.12</v>
       </c>
       <c r="T15" t="n">
         <v>100</v>
@@ -3369,7 +3369,7 @@
         <v>0.716</v>
       </c>
       <c r="S16" t="n">
-        <v>1.649</v>
+        <v>16.49</v>
       </c>
       <c r="T16" t="n">
         <v>100</v>

--- a/docs/tables/FINAL_results.xlsx
+++ b/docs/tables/FINAL_results.xlsx
@@ -645,59 +645,59 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>mast3r_ga</t>
+          <t>colmap</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>3.36</v>
+        <v>2.67</v>
       </c>
       <c r="I5" t="n">
-        <v>1.31</v>
+        <v>4.03</v>
       </c>
       <c r="J5" t="n">
-        <v>19.08</v>
+        <v>19.28</v>
       </c>
       <c r="K5" t="n">
-        <v>38.7</v>
+        <v>50.6</v>
       </c>
       <c r="L5" t="n">
-        <v>44.6</v>
+        <v>56.8</v>
       </c>
       <c r="M5" t="n">
-        <v>79.2</v>
+        <v>39</v>
       </c>
       <c r="N5" t="n">
-        <v>57.1</v>
+        <v>46.3</v>
       </c>
       <c r="O5" t="n">
-        <v>68.59999999999999</v>
+        <v>81.3</v>
       </c>
       <c r="P5" t="n">
-        <v>92.2</v>
+        <v>59.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>78.7</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="R5" t="n">
-        <v>99.59999999999999</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="S5" t="n">
-        <v>99.2</v>
+        <v>93</v>
       </c>
       <c r="T5" t="n">
-        <v>99.40000000000001</v>
+        <v>96</v>
       </c>
       <c r="U5" t="n">
-        <v>42.3</v>
+        <v>49.7</v>
       </c>
       <c r="V5" t="n">
-        <v>1150918</v>
+        <v>624826</v>
       </c>
       <c r="W5" t="n">
-        <v>458520</v>
+        <v>118844</v>
       </c>
       <c r="X5" t="n">
-        <v>2.51</v>
+        <v>5.26</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -713,175 +713,175 @@
     <row r="6">
       <c r="G6" t="inlineStr">
         <is>
-          <t>vggt</t>
+          <t>hloc_colmap</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>4.75</v>
+        <v>3.09</v>
       </c>
       <c r="I6" t="n">
-        <v>0.71</v>
+        <v>3.7</v>
       </c>
       <c r="J6" t="n">
-        <v>20.04</v>
+        <v>19.75</v>
       </c>
       <c r="K6" t="n">
-        <v>18.7</v>
+        <v>42.8</v>
       </c>
       <c r="L6" t="n">
-        <v>28.6</v>
+        <v>48.3</v>
       </c>
       <c r="M6" t="n">
-        <v>96.40000000000001</v>
+        <v>40.5</v>
       </c>
       <c r="N6" t="n">
         <v>44.1</v>
       </c>
       <c r="O6" t="n">
-        <v>52.8</v>
+        <v>75.5</v>
       </c>
       <c r="P6" t="n">
-        <v>99.09999999999999</v>
+        <v>66.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>68.90000000000001</v>
+        <v>70.7</v>
       </c>
       <c r="R6" t="n">
-        <v>99.40000000000001</v>
+        <v>99.2</v>
       </c>
       <c r="S6" t="n">
-        <v>99.90000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="T6" t="n">
-        <v>99.59999999999999</v>
+        <v>95.3</v>
       </c>
       <c r="U6" t="n">
-        <v>55.5</v>
+        <v>51.2</v>
       </c>
       <c r="V6" t="n">
-        <v>6995057</v>
+        <v>789125</v>
       </c>
       <c r="W6" t="n">
-        <v>2432352</v>
+        <v>139982</v>
       </c>
       <c r="X6" t="n">
-        <v>2.88</v>
+        <v>5.64</v>
       </c>
     </row>
     <row r="7">
       <c r="G7" t="inlineStr">
         <is>
-          <t>colmap</t>
+          <t>mast3r_ga</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.67</v>
+        <v>3.36</v>
       </c>
       <c r="I7" t="n">
-        <v>4.03</v>
+        <v>1.31</v>
       </c>
       <c r="J7" t="n">
-        <v>19.28</v>
+        <v>19.08</v>
       </c>
       <c r="K7" t="n">
-        <v>50.6</v>
+        <v>38.7</v>
       </c>
       <c r="L7" t="n">
-        <v>56.8</v>
+        <v>44.6</v>
       </c>
       <c r="M7" t="n">
-        <v>39</v>
+        <v>79.2</v>
       </c>
       <c r="N7" t="n">
-        <v>46.3</v>
+        <v>57.1</v>
       </c>
       <c r="O7" t="n">
-        <v>81.3</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>59.8</v>
+        <v>92.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>68.90000000000001</v>
+        <v>78.7</v>
       </c>
       <c r="R7" t="n">
-        <v>99.09999999999999</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="S7" t="n">
-        <v>93</v>
+        <v>99.2</v>
       </c>
       <c r="T7" t="n">
-        <v>96</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>49.7</v>
+        <v>42.3</v>
       </c>
       <c r="V7" t="n">
-        <v>624826</v>
+        <v>1150918</v>
       </c>
       <c r="W7" t="n">
-        <v>118844</v>
+        <v>458520</v>
       </c>
       <c r="X7" t="n">
-        <v>5.26</v>
+        <v>2.51</v>
       </c>
     </row>
     <row r="8">
       <c r="G8" t="inlineStr">
         <is>
-          <t>hloc_colmap</t>
+          <t>vggt</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>3.09</v>
+        <v>4.75</v>
       </c>
       <c r="I8" t="n">
-        <v>3.7</v>
+        <v>0.71</v>
       </c>
       <c r="J8" t="n">
-        <v>19.75</v>
+        <v>20.04</v>
       </c>
       <c r="K8" t="n">
-        <v>42.8</v>
+        <v>18.7</v>
       </c>
       <c r="L8" t="n">
-        <v>48.3</v>
+        <v>28.6</v>
       </c>
       <c r="M8" t="n">
-        <v>40.5</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="N8" t="n">
         <v>44.1</v>
       </c>
       <c r="O8" t="n">
-        <v>75.5</v>
+        <v>52.8</v>
       </c>
       <c r="P8" t="n">
-        <v>66.5</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="Q8" t="n">
-        <v>70.7</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="R8" t="n">
-        <v>99.2</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="S8" t="n">
-        <v>91.7</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>95.3</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>51.2</v>
+        <v>55.5</v>
       </c>
       <c r="V8" t="n">
-        <v>789125</v>
+        <v>6995057</v>
       </c>
       <c r="W8" t="n">
-        <v>139982</v>
+        <v>2432352</v>
       </c>
       <c r="X8" t="n">
-        <v>5.64</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="9">
@@ -909,59 +909,59 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>mast3r_ga</t>
+          <t>colmap</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1.61</v>
+        <v>1.38</v>
       </c>
       <c r="I9" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="J9" t="n">
-        <v>16.09</v>
+        <v>14.82</v>
       </c>
       <c r="K9" t="n">
-        <v>42.3</v>
+        <v>40.5</v>
       </c>
       <c r="L9" t="n">
-        <v>79.90000000000001</v>
+        <v>81.5</v>
       </c>
       <c r="M9" t="n">
-        <v>99.09999999999999</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>88.5</v>
+        <v>85.3</v>
       </c>
       <c r="O9" t="n">
-        <v>100</v>
+        <v>99.7</v>
       </c>
       <c r="P9" t="n">
-        <v>100</v>
+        <v>95.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>100</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="R9" t="n">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="S9" t="n">
-        <v>100</v>
+        <v>99.7</v>
       </c>
       <c r="T9" t="n">
-        <v>100</v>
+        <v>99.8</v>
       </c>
       <c r="U9" t="n">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="V9" t="n">
-        <v>734656</v>
+        <v>1123433</v>
       </c>
       <c r="W9" t="n">
-        <v>70153</v>
+        <v>36738</v>
       </c>
       <c r="X9" t="n">
-        <v>10.47</v>
+        <v>30.58</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -977,175 +977,175 @@
     <row r="10">
       <c r="G10" t="inlineStr">
         <is>
-          <t>vggt</t>
+          <t>hloc_colmap</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>2.84</v>
+        <v>1.61</v>
       </c>
       <c r="I10" t="n">
-        <v>0.63</v>
+        <v>0.91</v>
       </c>
       <c r="J10" t="n">
-        <v>19.77</v>
+        <v>15.7</v>
       </c>
       <c r="K10" t="n">
-        <v>24.2</v>
+        <v>35.6</v>
       </c>
       <c r="L10" t="n">
-        <v>54</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>99.40000000000001</v>
+        <v>86.3</v>
       </c>
       <c r="N10" t="n">
-        <v>70</v>
+        <v>80.8</v>
       </c>
       <c r="O10" t="n">
         <v>99.8</v>
       </c>
       <c r="P10" t="n">
-        <v>100</v>
+        <v>92.3</v>
       </c>
       <c r="Q10" t="n">
-        <v>99.90000000000001</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="R10" t="n">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="S10" t="n">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="U10" t="n">
-        <v>30</v>
+        <v>18.2</v>
       </c>
       <c r="V10" t="n">
-        <v>3334257</v>
+        <v>1064834</v>
       </c>
       <c r="W10" t="n">
-        <v>161957</v>
+        <v>37804</v>
       </c>
       <c r="X10" t="n">
-        <v>20.59</v>
+        <v>28.17</v>
       </c>
     </row>
     <row r="11">
       <c r="G11" t="inlineStr">
         <is>
-          <t>colmap</t>
+          <t>mast3r_ga</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1.38</v>
+        <v>1.61</v>
       </c>
       <c r="I11" t="n">
-        <v>0.58</v>
+        <v>0.64</v>
       </c>
       <c r="J11" t="n">
-        <v>14.82</v>
+        <v>16.09</v>
       </c>
       <c r="K11" t="n">
-        <v>40.5</v>
+        <v>42.3</v>
       </c>
       <c r="L11" t="n">
-        <v>81.5</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>89.40000000000001</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>85.3</v>
+        <v>88.5</v>
       </c>
       <c r="O11" t="n">
-        <v>99.7</v>
+        <v>100</v>
       </c>
       <c r="P11" t="n">
-        <v>95.2</v>
+        <v>100</v>
       </c>
       <c r="Q11" t="n">
-        <v>97.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="R11" t="n">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="S11" t="n">
-        <v>99.7</v>
+        <v>100</v>
       </c>
       <c r="T11" t="n">
-        <v>99.8</v>
+        <v>100</v>
       </c>
       <c r="U11" t="n">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="V11" t="n">
-        <v>1123433</v>
+        <v>734656</v>
       </c>
       <c r="W11" t="n">
-        <v>36738</v>
+        <v>70153</v>
       </c>
       <c r="X11" t="n">
-        <v>30.58</v>
+        <v>10.47</v>
       </c>
     </row>
     <row r="12">
       <c r="G12" t="inlineStr">
         <is>
-          <t>hloc_colmap</t>
+          <t>vggt</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1.61</v>
+        <v>2.84</v>
       </c>
       <c r="I12" t="n">
-        <v>0.91</v>
+        <v>0.63</v>
       </c>
       <c r="J12" t="n">
-        <v>15.7</v>
+        <v>19.77</v>
       </c>
       <c r="K12" t="n">
-        <v>35.6</v>
+        <v>24.2</v>
       </c>
       <c r="L12" t="n">
-        <v>75.90000000000001</v>
+        <v>54</v>
       </c>
       <c r="M12" t="n">
-        <v>86.3</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="N12" t="n">
-        <v>80.8</v>
+        <v>70</v>
       </c>
       <c r="O12" t="n">
         <v>99.8</v>
       </c>
       <c r="P12" t="n">
-        <v>92.3</v>
+        <v>100</v>
       </c>
       <c r="Q12" t="n">
-        <v>95.90000000000001</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="R12" t="n">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="S12" t="n">
-        <v>98.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="T12" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="U12" t="n">
-        <v>18.2</v>
+        <v>30</v>
       </c>
       <c r="V12" t="n">
-        <v>1064834</v>
+        <v>3334257</v>
       </c>
       <c r="W12" t="n">
-        <v>37804</v>
+        <v>161957</v>
       </c>
       <c r="X12" t="n">
-        <v>28.17</v>
+        <v>20.59</v>
       </c>
     </row>
     <row r="13">
@@ -1173,59 +1173,59 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>mast3r_ga</t>
+          <t>colmap</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="I13" t="n">
-        <v>1.48</v>
+        <v>1.69</v>
       </c>
       <c r="J13" t="n">
-        <v>19.55</v>
+        <v>19.87</v>
       </c>
       <c r="K13" t="n">
-        <v>56.1</v>
+        <v>56.2</v>
       </c>
       <c r="L13" t="n">
-        <v>66.2</v>
+        <v>66.7</v>
       </c>
       <c r="M13" t="n">
-        <v>71.7</v>
+        <v>67.2</v>
       </c>
       <c r="N13" t="n">
-        <v>68.8</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>85.40000000000001</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="Q13" t="n">
-        <v>92.09999999999999</v>
+        <v>86.7</v>
       </c>
       <c r="R13" t="n">
         <v>100</v>
       </c>
       <c r="S13" t="n">
-        <v>97.09999999999999</v>
+        <v>84.7</v>
       </c>
       <c r="T13" t="n">
-        <v>98.5</v>
+        <v>91.7</v>
       </c>
       <c r="U13" t="n">
-        <v>29.7</v>
+        <v>24.8</v>
       </c>
       <c r="V13" t="n">
-        <v>804316</v>
+        <v>1520520</v>
       </c>
       <c r="W13" t="n">
-        <v>136786</v>
+        <v>115064</v>
       </c>
       <c r="X13" t="n">
-        <v>5.88</v>
+        <v>13.21</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1241,175 +1241,175 @@
     <row r="14">
       <c r="G14" t="inlineStr">
         <is>
-          <t>vggt</t>
+          <t>hloc_colmap</t>
         </is>
       </c>
       <c r="H14" t="n">
         <v>2.81</v>
       </c>
       <c r="I14" t="n">
-        <v>1.11</v>
+        <v>2.8</v>
       </c>
       <c r="J14" t="n">
-        <v>20.86</v>
+        <v>21.7</v>
       </c>
       <c r="K14" t="n">
-        <v>39.5</v>
+        <v>50.5</v>
       </c>
       <c r="L14" t="n">
-        <v>55.8</v>
+        <v>57.3</v>
       </c>
       <c r="M14" t="n">
-        <v>84.5</v>
+        <v>54.6</v>
       </c>
       <c r="N14" t="n">
-        <v>67.2</v>
+        <v>55.9</v>
       </c>
       <c r="O14" t="n">
-        <v>99.8</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>93.8</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="Q14" t="n">
-        <v>96.7</v>
+        <v>86.3</v>
       </c>
       <c r="R14" t="n">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="S14" t="n">
-        <v>99.40000000000001</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>99.7</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>32.5</v>
+        <v>36.2</v>
       </c>
       <c r="V14" t="n">
-        <v>6726594</v>
+        <v>1462675</v>
       </c>
       <c r="W14" t="n">
-        <v>359926</v>
+        <v>103983</v>
       </c>
       <c r="X14" t="n">
-        <v>18.69</v>
+        <v>14.07</v>
       </c>
     </row>
     <row r="15">
       <c r="G15" t="inlineStr">
         <is>
-          <t>colmap</t>
+          <t>mast3r_ga</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="I15" t="n">
-        <v>1.69</v>
+        <v>1.48</v>
       </c>
       <c r="J15" t="n">
-        <v>19.87</v>
+        <v>19.55</v>
       </c>
       <c r="K15" t="n">
-        <v>56.2</v>
+        <v>56.1</v>
       </c>
       <c r="L15" t="n">
-        <v>66.7</v>
+        <v>66.2</v>
       </c>
       <c r="M15" t="n">
-        <v>67.2</v>
+        <v>71.7</v>
       </c>
       <c r="N15" t="n">
-        <v>66.90000000000001</v>
+        <v>68.8</v>
       </c>
       <c r="O15" t="n">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="P15" t="n">
-        <v>76.59999999999999</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="Q15" t="n">
-        <v>86.7</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="R15" t="n">
         <v>100</v>
       </c>
       <c r="S15" t="n">
-        <v>84.7</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>91.7</v>
+        <v>98.5</v>
       </c>
       <c r="U15" t="n">
-        <v>24.8</v>
+        <v>29.7</v>
       </c>
       <c r="V15" t="n">
-        <v>1520520</v>
+        <v>804316</v>
       </c>
       <c r="W15" t="n">
-        <v>115064</v>
+        <v>136786</v>
       </c>
       <c r="X15" t="n">
-        <v>13.21</v>
+        <v>5.88</v>
       </c>
     </row>
     <row r="16">
       <c r="G16" t="inlineStr">
         <is>
-          <t>hloc_colmap</t>
+          <t>vggt</t>
         </is>
       </c>
       <c r="H16" t="n">
         <v>2.81</v>
       </c>
       <c r="I16" t="n">
-        <v>2.8</v>
+        <v>1.11</v>
       </c>
       <c r="J16" t="n">
-        <v>21.7</v>
+        <v>20.86</v>
       </c>
       <c r="K16" t="n">
-        <v>50.5</v>
+        <v>39.5</v>
       </c>
       <c r="L16" t="n">
-        <v>57.3</v>
+        <v>55.8</v>
       </c>
       <c r="M16" t="n">
-        <v>54.6</v>
+        <v>84.5</v>
       </c>
       <c r="N16" t="n">
-        <v>55.9</v>
+        <v>67.2</v>
       </c>
       <c r="O16" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="P16" t="n">
+        <v>93.8</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>96.7</v>
+      </c>
+      <c r="R16" t="n">
         <v>99.90000000000001</v>
       </c>
-      <c r="P16" t="n">
-        <v>75.90000000000001</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>86.3</v>
-      </c>
-      <c r="R16" t="n">
-        <v>100</v>
-      </c>
       <c r="S16" t="n">
-        <v>85.40000000000001</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>92.09999999999999</v>
+        <v>99.7</v>
       </c>
       <c r="U16" t="n">
-        <v>36.2</v>
+        <v>32.5</v>
       </c>
       <c r="V16" t="n">
-        <v>1462675</v>
+        <v>6726594</v>
       </c>
       <c r="W16" t="n">
-        <v>103983</v>
+        <v>359926</v>
       </c>
       <c r="X16" t="n">
-        <v>14.07</v>
+        <v>18.69</v>
       </c>
     </row>
     <row r="17">
@@ -1437,59 +1437,59 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>mast3r_ga</t>
+          <t>colmap</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="I17" t="n">
-        <v>0.61</v>
+        <v>1.21</v>
       </c>
       <c r="J17" t="n">
-        <v>12.82</v>
+        <v>12.68</v>
       </c>
       <c r="K17" t="n">
-        <v>72.2</v>
+        <v>68.2</v>
       </c>
       <c r="L17" t="n">
-        <v>91.3</v>
+        <v>87.5</v>
       </c>
       <c r="M17" t="n">
-        <v>97</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="N17" t="n">
-        <v>94</v>
+        <v>83.8</v>
       </c>
       <c r="O17" t="n">
-        <v>100</v>
+        <v>99.7</v>
       </c>
       <c r="P17" t="n">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>99.3</v>
+      </c>
+      <c r="R17" t="n">
         <v>99.90000000000001</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="S17" t="n">
+        <v>100</v>
+      </c>
+      <c r="T17" t="n">
         <v>99.90000000000001</v>
       </c>
-      <c r="R17" t="n">
-        <v>100</v>
-      </c>
-      <c r="S17" t="n">
-        <v>100</v>
-      </c>
-      <c r="T17" t="n">
-        <v>100</v>
-      </c>
       <c r="U17" t="n">
-        <v>6</v>
+        <v>16.1</v>
       </c>
       <c r="V17" t="n">
-        <v>533608</v>
+        <v>214105</v>
       </c>
       <c r="W17" t="n">
-        <v>14002</v>
+        <v>6021</v>
       </c>
       <c r="X17" t="n">
-        <v>38.11</v>
+        <v>35.56</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -1505,38 +1505,38 @@
     <row r="18">
       <c r="G18" t="inlineStr">
         <is>
-          <t>vggt</t>
+          <t>hloc_colmap</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1.31</v>
+        <v>0.95</v>
       </c>
       <c r="I18" t="n">
-        <v>0.63</v>
+        <v>0.89</v>
       </c>
       <c r="J18" t="n">
-        <v>14.65</v>
+        <v>12.19</v>
       </c>
       <c r="K18" t="n">
-        <v>64</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>86.40000000000001</v>
+        <v>88.3</v>
       </c>
       <c r="M18" t="n">
-        <v>97</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="N18" t="n">
-        <v>91.40000000000001</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="O18" t="n">
-        <v>100</v>
+        <v>99.7</v>
       </c>
       <c r="P18" t="n">
-        <v>100</v>
+        <v>99.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>100</v>
+        <v>99.5</v>
       </c>
       <c r="R18" t="n">
         <v>100</v>
@@ -1548,111 +1548,111 @@
         <v>100</v>
       </c>
       <c r="U18" t="n">
-        <v>8.6</v>
+        <v>10.9</v>
       </c>
       <c r="V18" t="n">
-        <v>3697595</v>
+        <v>308184</v>
       </c>
       <c r="W18" t="n">
-        <v>28592</v>
+        <v>7106</v>
       </c>
       <c r="X18" t="n">
-        <v>129.32</v>
+        <v>43.37</v>
       </c>
     </row>
     <row r="19">
       <c r="G19" t="inlineStr">
         <is>
-          <t>colmap</t>
+          <t>mast3r_ga</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="I19" t="n">
-        <v>1.21</v>
+        <v>0.61</v>
       </c>
       <c r="J19" t="n">
-        <v>12.68</v>
+        <v>12.82</v>
       </c>
       <c r="K19" t="n">
-        <v>68.2</v>
+        <v>72.2</v>
       </c>
       <c r="L19" t="n">
-        <v>87.5</v>
+        <v>91.3</v>
       </c>
       <c r="M19" t="n">
-        <v>80.40000000000001</v>
+        <v>97</v>
       </c>
       <c r="N19" t="n">
-        <v>83.8</v>
+        <v>94</v>
       </c>
       <c r="O19" t="n">
-        <v>99.7</v>
+        <v>100</v>
       </c>
       <c r="P19" t="n">
-        <v>98.90000000000001</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="Q19" t="n">
-        <v>99.3</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="R19" t="n">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="S19" t="n">
         <v>100</v>
       </c>
       <c r="T19" t="n">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="U19" t="n">
-        <v>16.1</v>
+        <v>6</v>
       </c>
       <c r="V19" t="n">
-        <v>214105</v>
+        <v>533608</v>
       </c>
       <c r="W19" t="n">
-        <v>6021</v>
+        <v>14002</v>
       </c>
       <c r="X19" t="n">
-        <v>35.56</v>
+        <v>38.11</v>
       </c>
     </row>
     <row r="20">
       <c r="G20" t="inlineStr">
         <is>
-          <t>hloc_colmap</t>
+          <t>vggt</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>0.95</v>
+        <v>1.31</v>
       </c>
       <c r="I20" t="n">
-        <v>0.89</v>
+        <v>0.63</v>
       </c>
       <c r="J20" t="n">
-        <v>12.19</v>
+        <v>14.65</v>
       </c>
       <c r="K20" t="n">
-        <v>69.59999999999999</v>
+        <v>64</v>
       </c>
       <c r="L20" t="n">
-        <v>88.3</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>89.90000000000001</v>
+        <v>97</v>
       </c>
       <c r="N20" t="n">
-        <v>89.09999999999999</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="O20" t="n">
-        <v>99.7</v>
+        <v>100</v>
       </c>
       <c r="P20" t="n">
-        <v>99.3</v>
+        <v>100</v>
       </c>
       <c r="Q20" t="n">
-        <v>99.5</v>
+        <v>100</v>
       </c>
       <c r="R20" t="n">
         <v>100</v>
@@ -1664,16 +1664,16 @@
         <v>100</v>
       </c>
       <c r="U20" t="n">
-        <v>10.9</v>
+        <v>8.6</v>
       </c>
       <c r="V20" t="n">
-        <v>308184</v>
+        <v>3697595</v>
       </c>
       <c r="W20" t="n">
-        <v>7106</v>
+        <v>28592</v>
       </c>
       <c r="X20" t="n">
-        <v>43.37</v>
+        <v>129.32</v>
       </c>
     </row>
     <row r="21">
@@ -1701,59 +1701,59 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>mast3r_ga</t>
+          <t>colmap</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>3.48</v>
+        <v>0.98</v>
       </c>
       <c r="I21" t="n">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="J21" t="n">
-        <v>16.84</v>
+        <v>11.59</v>
       </c>
       <c r="K21" t="n">
-        <v>44.5</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>44.5</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="M21" t="n">
-        <v>88.8</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="N21" t="n">
-        <v>59.3</v>
+        <v>89.2</v>
       </c>
       <c r="O21" t="n">
-        <v>64.3</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="P21" t="n">
-        <v>96.5</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="Q21" t="n">
-        <v>77.2</v>
+        <v>95</v>
       </c>
       <c r="R21" t="n">
-        <v>87.5</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="S21" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="T21" t="n">
-        <v>93.3</v>
+        <v>99</v>
       </c>
       <c r="U21" t="n">
-        <v>34</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="V21" t="n">
-        <v>177102</v>
+        <v>133185</v>
       </c>
       <c r="W21" t="n">
-        <v>46577</v>
+        <v>18583</v>
       </c>
       <c r="X21" t="n">
-        <v>3.8</v>
+        <v>7.17</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -1769,175 +1769,175 @@
     <row r="22">
       <c r="G22" t="inlineStr">
         <is>
-          <t>vggt</t>
+          <t>hloc_colmap</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>10.66</v>
+        <v>1.05</v>
       </c>
       <c r="I22" t="n">
-        <v>1.17</v>
+        <v>1.65</v>
       </c>
       <c r="J22" t="n">
-        <v>17.59</v>
+        <v>13</v>
       </c>
       <c r="K22" t="n">
-        <v>12.3</v>
+        <v>91.7</v>
       </c>
       <c r="L22" t="n">
-        <v>12.3</v>
+        <v>91.7</v>
       </c>
       <c r="M22" t="n">
-        <v>96</v>
+        <v>75.2</v>
       </c>
       <c r="N22" t="n">
-        <v>21.8</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="O22" t="n">
-        <v>20.9</v>
+        <v>97.5</v>
       </c>
       <c r="P22" t="n">
-        <v>99</v>
+        <v>84.8</v>
       </c>
       <c r="Q22" t="n">
-        <v>34.5</v>
+        <v>90.8</v>
       </c>
       <c r="R22" t="n">
-        <v>46.5</v>
+        <v>99.8</v>
       </c>
       <c r="S22" t="n">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="T22" t="n">
-        <v>63.4</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="U22" t="n">
-        <v>41.6</v>
+        <v>11.5</v>
       </c>
       <c r="V22" t="n">
-        <v>293168</v>
+        <v>59502</v>
       </c>
       <c r="W22" t="n">
-        <v>152549</v>
+        <v>10543</v>
       </c>
       <c r="X22" t="n">
-        <v>1.92</v>
+        <v>5.64</v>
       </c>
     </row>
     <row r="23">
       <c r="G23" t="inlineStr">
         <is>
-          <t>colmap</t>
+          <t>mast3r_ga</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>0.98</v>
+        <v>3.48</v>
       </c>
       <c r="I23" t="n">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="J23" t="n">
-        <v>11.59</v>
+        <v>16.84</v>
       </c>
       <c r="K23" t="n">
-        <v>96.59999999999999</v>
+        <v>44.5</v>
       </c>
       <c r="L23" t="n">
-        <v>96.59999999999999</v>
+        <v>44.5</v>
       </c>
       <c r="M23" t="n">
-        <v>82.90000000000001</v>
+        <v>88.8</v>
       </c>
       <c r="N23" t="n">
-        <v>89.2</v>
+        <v>59.3</v>
       </c>
       <c r="O23" t="n">
-        <v>99.40000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="P23" t="n">
-        <v>90.90000000000001</v>
+        <v>96.5</v>
       </c>
       <c r="Q23" t="n">
-        <v>95</v>
+        <v>77.2</v>
       </c>
       <c r="R23" t="n">
-        <v>99.90000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="S23" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="T23" t="n">
-        <v>99</v>
+        <v>93.3</v>
       </c>
       <c r="U23" t="n">
-        <v>9.800000000000001</v>
+        <v>34</v>
       </c>
       <c r="V23" t="n">
-        <v>133185</v>
+        <v>177102</v>
       </c>
       <c r="W23" t="n">
-        <v>18583</v>
+        <v>46577</v>
       </c>
       <c r="X23" t="n">
-        <v>7.17</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="24">
       <c r="G24" t="inlineStr">
         <is>
-          <t>hloc_colmap</t>
+          <t>vggt</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>1.05</v>
+        <v>10.66</v>
       </c>
       <c r="I24" t="n">
-        <v>1.65</v>
+        <v>1.17</v>
       </c>
       <c r="J24" t="n">
-        <v>13</v>
+        <v>17.59</v>
       </c>
       <c r="K24" t="n">
-        <v>91.7</v>
+        <v>12.3</v>
       </c>
       <c r="L24" t="n">
-        <v>91.7</v>
+        <v>12.3</v>
       </c>
       <c r="M24" t="n">
-        <v>75.2</v>
+        <v>96</v>
       </c>
       <c r="N24" t="n">
-        <v>82.59999999999999</v>
+        <v>21.8</v>
       </c>
       <c r="O24" t="n">
-        <v>97.5</v>
+        <v>20.9</v>
       </c>
       <c r="P24" t="n">
-        <v>84.8</v>
+        <v>99</v>
       </c>
       <c r="Q24" t="n">
-        <v>90.8</v>
+        <v>34.5</v>
       </c>
       <c r="R24" t="n">
-        <v>99.8</v>
+        <v>46.5</v>
       </c>
       <c r="S24" t="n">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="T24" t="n">
-        <v>94.09999999999999</v>
+        <v>63.4</v>
       </c>
       <c r="U24" t="n">
-        <v>11.5</v>
+        <v>41.6</v>
       </c>
       <c r="V24" t="n">
-        <v>59502</v>
+        <v>293168</v>
       </c>
       <c r="W24" t="n">
-        <v>10543</v>
+        <v>152549</v>
       </c>
       <c r="X24" t="n">
-        <v>5.64</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="25">
@@ -1965,59 +1965,59 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>mast3r_ga</t>
+          <t>colmap</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>8.31</v>
+        <v>2.49</v>
       </c>
       <c r="I25" t="n">
-        <v>1.3</v>
+        <v>1.88</v>
       </c>
       <c r="J25" t="n">
-        <v>17.87</v>
+        <v>17.77</v>
       </c>
       <c r="K25" t="n">
-        <v>28.6</v>
+        <v>58.8</v>
       </c>
       <c r="L25" t="n">
-        <v>28.6</v>
+        <v>58.8</v>
       </c>
       <c r="M25" t="n">
-        <v>83.3</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="N25" t="n">
-        <v>42.6</v>
+        <v>67.2</v>
       </c>
       <c r="O25" t="n">
-        <v>40.8</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="P25" t="n">
-        <v>95.09999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="Q25" t="n">
-        <v>57.1</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="R25" t="n">
-        <v>53.6</v>
+        <v>89.5</v>
       </c>
       <c r="S25" t="n">
-        <v>100</v>
+        <v>99.8</v>
       </c>
       <c r="T25" t="n">
-        <v>69.8</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="U25" t="n">
         <v>27.2</v>
       </c>
       <c r="V25" t="n">
-        <v>569403</v>
+        <v>327676</v>
       </c>
       <c r="W25" t="n">
-        <v>130311</v>
+        <v>29266</v>
       </c>
       <c r="X25" t="n">
-        <v>4.37</v>
+        <v>11.2</v>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
@@ -2033,175 +2033,175 @@
     <row r="26">
       <c r="G26" t="inlineStr">
         <is>
-          <t>vggt</t>
+          <t>hloc_colmap</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>4.5</v>
+        <v>2.78</v>
       </c>
       <c r="I26" t="n">
-        <v>0.58</v>
+        <v>2.16</v>
       </c>
       <c r="J26" t="n">
-        <v>18.17</v>
+        <v>16.59</v>
       </c>
       <c r="K26" t="n">
-        <v>35.5</v>
+        <v>52.7</v>
       </c>
       <c r="L26" t="n">
-        <v>35.5</v>
+        <v>52.7</v>
       </c>
       <c r="M26" t="n">
-        <v>99.59999999999999</v>
+        <v>64.3</v>
       </c>
       <c r="N26" t="n">
-        <v>52.4</v>
+        <v>58</v>
       </c>
       <c r="O26" t="n">
-        <v>54</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="P26" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="Q26" t="n">
-        <v>70.09999999999999</v>
+        <v>79.2</v>
       </c>
       <c r="R26" t="n">
-        <v>80.90000000000001</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="S26" t="n">
-        <v>100</v>
+        <v>99.8</v>
       </c>
       <c r="T26" t="n">
-        <v>89.40000000000001</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="U26" t="n">
-        <v>37</v>
+        <v>34.9</v>
       </c>
       <c r="V26" t="n">
-        <v>2881563</v>
+        <v>261293</v>
       </c>
       <c r="W26" t="n">
-        <v>322936</v>
+        <v>23147</v>
       </c>
       <c r="X26" t="n">
-        <v>8.92</v>
+        <v>11.29</v>
       </c>
     </row>
     <row r="27">
       <c r="G27" t="inlineStr">
         <is>
-          <t>colmap</t>
+          <t>mast3r_ga</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>2.49</v>
+        <v>8.31</v>
       </c>
       <c r="I27" t="n">
-        <v>1.88</v>
+        <v>1.3</v>
       </c>
       <c r="J27" t="n">
-        <v>17.77</v>
+        <v>17.87</v>
       </c>
       <c r="K27" t="n">
-        <v>58.8</v>
+        <v>28.6</v>
       </c>
       <c r="L27" t="n">
-        <v>58.8</v>
+        <v>28.6</v>
       </c>
       <c r="M27" t="n">
-        <v>78.40000000000001</v>
+        <v>83.3</v>
       </c>
       <c r="N27" t="n">
-        <v>67.2</v>
+        <v>42.6</v>
       </c>
       <c r="O27" t="n">
-        <v>76.59999999999999</v>
+        <v>40.8</v>
       </c>
       <c r="P27" t="n">
-        <v>95.2</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="Q27" t="n">
-        <v>84.90000000000001</v>
+        <v>57.1</v>
       </c>
       <c r="R27" t="n">
-        <v>89.5</v>
+        <v>53.6</v>
       </c>
       <c r="S27" t="n">
-        <v>99.8</v>
+        <v>100</v>
       </c>
       <c r="T27" t="n">
-        <v>94.40000000000001</v>
+        <v>69.8</v>
       </c>
       <c r="U27" t="n">
         <v>27.2</v>
       </c>
       <c r="V27" t="n">
-        <v>327676</v>
+        <v>569403</v>
       </c>
       <c r="W27" t="n">
-        <v>29266</v>
+        <v>130311</v>
       </c>
       <c r="X27" t="n">
-        <v>11.2</v>
+        <v>4.37</v>
       </c>
     </row>
     <row r="28">
       <c r="G28" t="inlineStr">
         <is>
-          <t>hloc_colmap</t>
+          <t>vggt</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>2.78</v>
+        <v>4.5</v>
       </c>
       <c r="I28" t="n">
-        <v>2.16</v>
+        <v>0.58</v>
       </c>
       <c r="J28" t="n">
-        <v>16.59</v>
+        <v>18.17</v>
       </c>
       <c r="K28" t="n">
-        <v>52.7</v>
+        <v>35.5</v>
       </c>
       <c r="L28" t="n">
-        <v>52.7</v>
+        <v>35.5</v>
       </c>
       <c r="M28" t="n">
-        <v>64.3</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="N28" t="n">
-        <v>58</v>
+        <v>52.4</v>
       </c>
       <c r="O28" t="n">
-        <v>73.40000000000001</v>
+        <v>54</v>
       </c>
       <c r="P28" t="n">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="Q28" t="n">
-        <v>79.2</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="R28" t="n">
-        <v>86.90000000000001</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="S28" t="n">
-        <v>99.8</v>
+        <v>100</v>
       </c>
       <c r="T28" t="n">
-        <v>92.90000000000001</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="U28" t="n">
-        <v>34.9</v>
+        <v>37</v>
       </c>
       <c r="V28" t="n">
-        <v>261293</v>
+        <v>2881563</v>
       </c>
       <c r="W28" t="n">
-        <v>23147</v>
+        <v>322936</v>
       </c>
       <c r="X28" t="n">
-        <v>11.29</v>
+        <v>8.92</v>
       </c>
     </row>
   </sheetData>
